--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104694_W27.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104694_W27.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0807</v>
+        <v>5.3039</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6802</v>
+        <v>3.2447</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4005</v>
+        <v>2.0593</v>
       </c>
       <c r="G2" t="n">
-        <v>3.5098</v>
+        <v>3.5012</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4057</v>
+        <v>3.3845</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1041</v>
+        <v>0.1168</v>
       </c>
       <c r="J2" t="n">
-        <v>4.146</v>
+        <v>4.1137</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8474</v>
+        <v>3.8159</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2985</v>
+        <v>0.2979</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6362</v>
+        <v>-0.6125</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4417</v>
+        <v>-0.4314</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5975</v>
+        <v>0.8223</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6684</v>
+        <v>0.2691</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9291</v>
+        <v>0.5532</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4686</v>
+        <v>4.4472</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9343</v>
+        <v>4.4969</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4657</v>
+        <v>-0.0497</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4786</v>
+        <v>1.4587</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2725</v>
+        <v>-0.2837</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7512</v>
+        <v>1.7425</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2661</v>
+        <v>3.2172</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5155</v>
+        <v>0.4924</v>
       </c>
       <c r="L3" t="n">
-        <v>2.7506</v>
+        <v>2.7249</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7875</v>
+        <v>-1.7585</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.788</v>
+        <v>-0.7761</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9994</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1506</v>
+        <v>0.1462</v>
       </c>
       <c r="T3" t="n">
-        <v>0.617</v>
+        <v>0.2388</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4664</v>
+        <v>-0.0926</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4783</v>
+        <v>1.4764</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9724</v>
+        <v>3.6511</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1781</v>
+        <v>2.7908</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7943</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.686</v>
+        <v>-1.6959</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.8858</v>
+        <v>-1.8923</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1999</v>
+        <v>0.1965</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1684</v>
+        <v>0.1352</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.1296</v>
+        <v>-1.1451</v>
       </c>
       <c r="L4" t="n">
-        <v>1.298</v>
+        <v>1.2803</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.8543</v>
+        <v>-1.831</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0981</v>
+        <v>-1.0838</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5024</v>
+        <v>0.1892</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8166</v>
+        <v>-0.156</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3142</v>
+        <v>0.3452</v>
       </c>
       <c r="V4" t="n">
-        <v>2.8924</v>
+        <v>2.8814</v>
       </c>
       <c r="W4" t="n">
-        <v>3.0531</v>
+        <v>3.0392</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. GUERRERO</t>
+          <t>C. ORTEGA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0588</v>
+        <v>0.6694</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1098</v>
+        <v>0.1979</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.051</v>
+        <v>0.4714</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4968</v>
+        <v>0.1387</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9206</v>
+        <v>0.1952</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4238</v>
+        <v>-0.0565</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7227</v>
+        <v>0.0517</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1256</v>
+        <v>0.0517</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5971</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2258</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.205</v>
+        <v>0.1435</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0209</v>
+        <v>-0.0565</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="S5" t="n">
-        <v>1.201</v>
+        <v>0.3031</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3871</v>
+        <v>0.1462</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8139</v>
+        <v>0.1568</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. LUZ</t>
+          <t>R. GUERRERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4116</v>
+        <v>0.628</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5505</v>
+        <v>2.0086</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1389</v>
+        <v>-1.3807</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.5147</v>
+        <v>0.4992</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.6479</v>
+        <v>0.9191</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1333</v>
+        <v>-0.4199</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3266</v>
+        <v>1.7162</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7344000000000001</v>
+        <v>1.1204</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4078</v>
+        <v>0.5958</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.188</v>
+        <v>-1.2169</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9135</v>
+        <v>-0.2012</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2745</v>
+        <v>-1.0157</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2458</v>
+        <v>0.763</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8771</v>
+        <v>0.2925</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3687</v>
+        <v>0.4705</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. ORTEGA</t>
+          <t>R. LUZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.0497</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2959</v>
+        <v>0.1422</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3722</v>
+        <v>-0.0924</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1347</v>
+        <v>-1.5121</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1933</v>
+        <v>-1.6431</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0586</v>
+        <v>0.131</v>
       </c>
       <c r="J7" t="n">
-        <v>0.052</v>
+        <v>-0.336</v>
       </c>
       <c r="K7" t="n">
-        <v>0.052</v>
+        <v>-0.7379</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.4019</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0828</v>
+        <v>-1.1761</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1414</v>
+        <v>-0.9052</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0586</v>
+        <v>-0.271</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2852</v>
+        <v>0.879</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3478</v>
+        <v>0.4782</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0626</v>
+        <v>0.4008</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. KOSTADINOV</t>
+          <t>Y. PONS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1543</v>
+        <v>-1.0534</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2552</v>
+        <v>-1.3103</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4094</v>
+        <v>0.2569</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2387</v>
+        <v>-1.7051</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0332</v>
+        <v>-0.3107</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2719</v>
+        <v>-1.3944</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4427</v>
+        <v>0.1837</v>
       </c>
       <c r="K8" t="n">
-        <v>1.368</v>
+        <v>0.8101</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0746</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2039</v>
+        <v>-1.8888</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4012</v>
+        <v>-1.1209</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1973</v>
+        <v>-0.768</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4537</v>
+        <v>2.9592</v>
       </c>
       <c r="S8" t="n">
-        <v>0.607</v>
+        <v>-0.0814</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1735</v>
+        <v>-0.1282</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5665</v>
+        <v>0.0468</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0927</v>
+        <v>-0.8603</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Y. PONS</t>
+          <t>K. KOSTADINOV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2887</v>
+        <v>-1.6906</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2498</v>
+        <v>0.609</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0389</v>
+        <v>-2.2996</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7119</v>
+        <v>0.2456</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3205</v>
+        <v>-0.0317</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3914</v>
+        <v>0.2773</v>
       </c>
       <c r="J9" t="n">
-        <v>0.206</v>
+        <v>1.4362</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8139</v>
+        <v>1.3617</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6079</v>
+        <v>0.0745</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9179</v>
+        <v>-1.1906</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1344</v>
+        <v>-1.3934</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7835</v>
+        <v>0.2028</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5878</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R9" t="n">
-        <v>2.9488</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2969</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0948</v>
+        <v>0.5386</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.202</v>
+        <v>-0.4749</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.8678</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8678</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1036</v>
+        <v>-2.1794</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2867</v>
+        <v>-0.4186</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8169</v>
+        <v>-1.7609</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9339</v>
+        <v>-0.9399</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0374</v>
+        <v>-2.0391</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1035</v>
+        <v>1.0991</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8909</v>
+        <v>0.8663</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4471</v>
+        <v>-0.4589</v>
       </c>
       <c r="L10" t="n">
-        <v>1.338</v>
+        <v>1.3252</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8248</v>
+        <v>-1.8062</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5903</v>
+        <v>-1.5802</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R10" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.077</v>
+        <v>-0.15</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8166</v>
+        <v>0.0809</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2604</v>
+        <v>-0.2309</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1265</v>
+        <v>-2.8008</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8697</v>
+        <v>-0.6292</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2568</v>
+        <v>-2.1715</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1962</v>
+        <v>-2.1991</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6204</v>
+        <v>-1.6226</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5758</v>
+        <v>-0.5765</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0481</v>
+        <v>-1.0679</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7069</v>
+        <v>-0.7174</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3413</v>
+        <v>-0.3505</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.148</v>
+        <v>-1.1312</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9135</v>
+        <v>-0.9052</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S11" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.418</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1785</v>
+        <v>0.4387</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0823</v>
+        <v>-0.0207</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. RICE</t>
+          <t>K. KURIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0199</v>
+        <v>-4.2391</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.286</v>
+        <v>-3.2494</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7339</v>
+        <v>-0.9898</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.5421</v>
+        <v>-3.0533</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.6705</v>
+        <v>-1.7321</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8716</v>
+        <v>-1.3213</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.8483</v>
+        <v>-2.1366</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.5043</v>
+        <v>-0.669</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.344</v>
+        <v>-1.4676</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.6938</v>
+        <v>-0.9167999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1662</v>
+        <v>-1.0631</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5276</v>
+        <v>0.1463</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.4952</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8147</v>
+        <v>0.4553</v>
       </c>
       <c r="S12" t="n">
-        <v>2.0666</v>
+        <v>-0.5029</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2824</v>
+        <v>0.0253</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7842</v>
+        <v>-0.5283</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.8639</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.2249</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K. KURIC</t>
+          <t>S. RICE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.8198</v>
+        <v>-4.8253</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.6593</v>
+        <v>-3.7295</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1605</v>
+        <v>-1.0958</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.058</v>
+        <v>-3.5623</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.7359</v>
+        <v>-2.6955</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.3221</v>
+        <v>-0.8667</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.1259</v>
+        <v>-1.9039</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6651</v>
+        <v>-1.5458</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.4608</v>
+        <v>-0.3581</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.9321</v>
+        <v>-1.6583</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.0708</v>
+        <v>-1.1497</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1387</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1342</v>
+        <v>-2.5039</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4537</v>
+        <v>1.8211</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0812</v>
+        <v>1.2833</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3992</v>
+        <v>0.9076</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6820000000000001</v>
+        <v>0.3757</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-1.8634</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-0.2292</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.444399999999999</v>
+        <v>-2.0393</v>
       </c>
       <c r="E14" t="n">
-        <v>3.060700000000001</v>
+        <v>4.153100000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.505</v>
+        <v>-6.192399999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-8.7842</v>
+        <v>-8.824300000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-7.7045</v>
+        <v>-7.752</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.0794</v>
+        <v>-1.0721</v>
       </c>
       <c r="J14" t="n">
-        <v>6.545900000000001</v>
+        <v>6.2758</v>
       </c>
       <c r="K14" t="n">
-        <v>2.535000000000001</v>
+        <v>2.3781</v>
       </c>
       <c r="L14" t="n">
-        <v>4.0106</v>
+        <v>3.8978</v>
       </c>
       <c r="M14" t="n">
-        <v>-15.3295</v>
+        <v>-15.0999</v>
       </c>
       <c r="N14" t="n">
-        <v>-10.2395</v>
+        <v>-10.1301</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.090099999999999</v>
+        <v>-4.97</v>
       </c>
       <c r="P14" t="n">
-        <v>5.670799999999999</v>
+        <v>5.690799999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-10.2076</v>
+        <v>-10.2435</v>
       </c>
       <c r="R14" t="n">
-        <v>15.8784</v>
+        <v>15.9342</v>
       </c>
       <c r="S14" t="n">
-        <v>2.722</v>
+        <v>4.1335</v>
       </c>
       <c r="T14" t="n">
-        <v>1.709</v>
+        <v>3.1317</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0131</v>
+        <v>1.0016</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.0532</v>
+        <v>-3.0394</v>
       </c>
       <c r="W14" t="n">
-        <v>5.013500000000001</v>
+        <v>4.9889</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.066799999999999</v>
+        <v>-8.0283</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6952</v>
+        <v>3.3261</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4723</v>
+        <v>1.0952</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2229</v>
+        <v>2.2309</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7651</v>
+        <v>2.7907</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0835</v>
+        <v>0.0969</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6816</v>
+        <v>2.6938</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8385</v>
+        <v>1.8264</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4951</v>
+        <v>0.4859</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3434</v>
+        <v>1.3405</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9266</v>
+        <v>0.9643</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4116</v>
+        <v>-0.389</v>
       </c>
       <c r="O15" t="n">
-        <v>1.3382</v>
+        <v>1.3532</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1645</v>
+        <v>-0.5525</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0998</v>
+        <v>-0.4533</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0648</v>
+        <v>-0.0992</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3139</v>
+        <v>2.9572</v>
       </c>
       <c r="E16" t="n">
-        <v>4.4142</v>
+        <v>3.6945</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1003</v>
+        <v>-0.7373</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2533</v>
+        <v>-0.2447</v>
       </c>
       <c r="H16" t="n">
-        <v>1.29</v>
+        <v>1.2923</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.5433</v>
+        <v>-1.537</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0897</v>
+        <v>1.0853</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8658</v>
+        <v>0.8618</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2239</v>
+        <v>0.2234</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3431</v>
+        <v>-1.33</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4241</v>
+        <v>0.4305</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.7672</v>
+        <v>-1.7604</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S16" t="n">
-        <v>1.087</v>
+        <v>0.727</v>
       </c>
       <c r="T16" t="n">
-        <v>1.364</v>
+        <v>0.6595</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.277</v>
+        <v>0.0675</v>
       </c>
       <c r="V16" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="W16" t="n">
-        <v>1.9604</v>
+        <v>1.9497</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2009</v>
+        <v>2.344</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2103</v>
+        <v>2.1701</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0094</v>
+        <v>0.1738</v>
       </c>
       <c r="G17" t="n">
-        <v>4.242</v>
+        <v>4.2393</v>
       </c>
       <c r="H17" t="n">
-        <v>3.3623</v>
+        <v>3.3495</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8797</v>
+        <v>0.8897</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4123</v>
+        <v>3.39</v>
       </c>
       <c r="K17" t="n">
-        <v>3.3004</v>
+        <v>3.2783</v>
       </c>
       <c r="L17" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8297</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0619</v>
+        <v>0.0713</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7678</v>
+        <v>0.778</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3871</v>
+        <v>-0.232</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3478</v>
+        <v>-0.3485</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0393</v>
+        <v>0.1165</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="18">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9188</v>
+        <v>1.4392</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9679</v>
+        <v>-0.624</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8867</v>
+        <v>2.0632</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2878</v>
+        <v>1.2973</v>
       </c>
       <c r="H18" t="n">
-        <v>0.704</v>
+        <v>0.7118</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5838</v>
+        <v>0.5855</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5836</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1385</v>
+        <v>0.1379</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4451</v>
+        <v>0.4392</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7042</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5655</v>
+        <v>0.574</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.369</v>
+        <v>0.1418</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4174</v>
+        <v>-0.0629</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0484</v>
+        <v>0.2047</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.799</v>
+        <v>1.1687</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3361</v>
+        <v>-1.0194</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1351</v>
+        <v>2.1881</v>
       </c>
       <c r="G19" t="n">
-        <v>2.1074</v>
+        <v>2.0953</v>
       </c>
       <c r="H19" t="n">
-        <v>2.9711</v>
+        <v>2.9671</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8637</v>
+        <v>-0.8718</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4191</v>
+        <v>1.3895</v>
       </c>
       <c r="K19" t="n">
-        <v>2.736</v>
+        <v>2.7234</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3169</v>
+        <v>-1.334</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6883</v>
+        <v>0.7058</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2351</v>
+        <v>0.2437</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1742</v>
+        <v>0.2115</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4869</v>
+        <v>-0.1326</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3127</v>
+        <v>0.3441</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. DIAGNE</t>
+          <t>M. FORREST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3546</v>
+        <v>0.9048</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7618</v>
+        <v>-1.6137</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4072</v>
+        <v>2.5184</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.4293</v>
+        <v>0.4378</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.4027</v>
+        <v>0.5572</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0266</v>
+        <v>-0.1194</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4812</v>
+        <v>-0.4404</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6304999999999999</v>
+        <v>0.1411</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1493</v>
+        <v>-0.5816</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.948</v>
+        <v>0.8782</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7721</v>
+        <v>0.416</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1759</v>
+        <v>0.4622</v>
       </c>
       <c r="P20" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S20" t="n">
-        <v>1.5155</v>
+        <v>0.0117</v>
       </c>
       <c r="T20" t="n">
-        <v>1.2431</v>
+        <v>-0.0351</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2725</v>
+        <v>0.0468</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. DEJULIUS</t>
+          <t>K. MARTIN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3524</v>
+        <v>0.6548</v>
       </c>
       <c r="E21" t="n">
-        <v>2.3022</v>
+        <v>1.9011</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9498</v>
+        <v>-1.2464</v>
       </c>
       <c r="G21" t="n">
-        <v>5.7763</v>
+        <v>-0.7894</v>
       </c>
       <c r="H21" t="n">
-        <v>2.1112</v>
+        <v>-2.1635</v>
       </c>
       <c r="I21" t="n">
-        <v>3.665</v>
+        <v>1.374</v>
       </c>
       <c r="J21" t="n">
-        <v>7.9468</v>
+        <v>1.186</v>
       </c>
       <c r="K21" t="n">
-        <v>3.0264</v>
+        <v>-1.1139</v>
       </c>
       <c r="L21" t="n">
-        <v>4.9204</v>
+        <v>2.2999</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.1706</v>
+        <v>-1.9754</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9152</v>
+        <v>-1.0496</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2554</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>-5.2172</v>
+        <v>0.9105</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.6708</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7531</v>
+        <v>-0.785</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5202</v>
+        <v>-0.3743</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2329</v>
+        <v>-0.4107</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5463</v>
+        <v>1.3187</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5463</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. FORREST</t>
+          <t>D. DEJULIUS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.161</v>
+        <v>0.5869</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1793</v>
+        <v>2.3435</v>
       </c>
       <c r="F22" t="n">
-        <v>2.3404</v>
+        <v>-1.7566</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4423</v>
+        <v>5.7583</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5570000000000001</v>
+        <v>2.1001</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1147</v>
+        <v>3.6582</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4191</v>
+        <v>7.8917</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1487</v>
+        <v>2.9917</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5679</v>
+        <v>4.8999</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8614000000000001</v>
+        <v>-2.1334</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4082</v>
+        <v>-0.8915999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4532</v>
+        <v>-1.2417</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4537</v>
+        <v>-5.2355</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-5.6908</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5878</v>
+        <v>0.4553</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7349</v>
+        <v>-0.4806</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6261</v>
+        <v>-0.4021</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1089</v>
+        <v>-0.0785</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>K. MARTIN</t>
+          <t>M. DIAGNE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1648</v>
+        <v>-0.0848</v>
       </c>
       <c r="E23" t="n">
-        <v>1.5934</v>
+        <v>0.1715</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7582</v>
+        <v>-0.2563</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7837</v>
+        <v>-1.4168</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.1776</v>
+        <v>-1.3962</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3939</v>
+        <v>-0.0206</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2296</v>
+        <v>-0.4856</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.1052</v>
+        <v>-0.6345</v>
       </c>
       <c r="L23" t="n">
-        <v>2.3347</v>
+        <v>0.1489</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.0133</v>
+        <v>-0.9312</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0725</v>
+        <v>-0.7617</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9408</v>
+        <v>-0.1695</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.606</v>
+        <v>1.0557</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7289</v>
+        <v>0.6571</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8771</v>
+        <v>0.3986</v>
       </c>
       <c r="V23" t="n">
-        <v>1.3176</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.2249</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.0347</v>
+        <v>-1.4598</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5042</v>
+        <v>0.0326</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5389</v>
+        <v>-1.4924</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.0042</v>
+        <v>-0.9871</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.2074</v>
+        <v>-1.2019</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1908</v>
+        <v>-1.1733</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.394</v>
+        <v>-1.3881</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2574</v>
+        <v>-0.7003</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3176</v>
+        <v>-0.1535</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.575</v>
+        <v>-0.5468</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.5598</v>
+        <v>-3.2322</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.6631</v>
+        <v>-0.346</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.8966</v>
+        <v>-2.8862</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.9182</v>
+        <v>-1.905</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5048</v>
+        <v>0.5218</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.423</v>
+        <v>-2.4268</v>
       </c>
       <c r="J25" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.056</v>
       </c>
       <c r="K25" t="n">
-        <v>1.2468</v>
+        <v>1.2411</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.1676</v>
+        <v>-1.185</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.9974</v>
+        <v>-1.961</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.742</v>
+        <v>-0.7193000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.2554</v>
+        <v>-1.2417</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8269</v>
+        <v>-0.5062</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6593</v>
+        <v>-0.3046</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1676</v>
+        <v>-0.2016</v>
       </c>
       <c r="V25" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W25" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="26">
@@ -2437,40 +2437,40 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.5921</v>
+        <v>-3.5922</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.6068</v>
+        <v>-1.6132</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.9853</v>
+        <v>-1.9789</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.4481</v>
+        <v>-2.4515</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.5022</v>
+        <v>-0.4999</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.9459</v>
+        <v>-1.9517</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.5554</v>
+        <v>-1.562</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.5727</v>
+        <v>-1.5793</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.8927</v>
+        <v>-0.8895</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.5195</v>
+        <v>-0.5171</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2482,22 +2482,22 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.0514</v>
+        <v>-0.0512</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.0514</v>
+        <v>-0.0512</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>3.444399999999999</v>
+        <v>5.012699999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>6.505200000000002</v>
+        <v>6.192200000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.0606</v>
+        <v>-1.179699999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>8.7841</v>
+        <v>8.824200000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>7.704700000000001</v>
+        <v>7.751900000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>1.0794</v>
+        <v>1.072</v>
       </c>
       <c r="J27" t="n">
-        <v>15.3297</v>
+        <v>15.1002</v>
       </c>
       <c r="K27" t="n">
-        <v>10.2393</v>
+        <v>10.13</v>
       </c>
       <c r="L27" t="n">
-        <v>5.0903</v>
+        <v>4.969800000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>-6.5457</v>
+        <v>-6.275900000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>-2.5348</v>
+        <v>-2.378000000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>-4.0108</v>
+        <v>-3.8978</v>
       </c>
       <c r="P27" t="n">
-        <v>-5.671</v>
+        <v>-5.6909</v>
       </c>
       <c r="Q27" t="n">
-        <v>-15.8783</v>
+        <v>-15.9343</v>
       </c>
       <c r="R27" t="n">
-        <v>10.2075</v>
+        <v>10.2435</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.722</v>
+        <v>-1.1601</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.0131</v>
+        <v>-1.0015</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.709</v>
+        <v>-0.1586</v>
       </c>
       <c r="V27" t="n">
-        <v>3.053</v>
+        <v>3.039199999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>8.066600000000001</v>
+        <v>8.0281</v>
       </c>
       <c r="X27" t="n">
-        <v>-5.0136</v>
+        <v>-4.989</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104694_W27.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104694_W27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104694_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104694_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104694_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104694_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104694_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104694_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104694_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104694_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104694_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104694_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104694_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104694_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-8.0283</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104694_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104694_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104694_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104694_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104694_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104694_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104694_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104694_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104694_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104694_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104694_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104694_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-4.989</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
